--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -259,7 +259,7 @@
     <t>薬の服用方法・服用した方法、または服用すべき方法</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -321,7 +321,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -512,15 +512,13 @@
     <t>投与タイミングを記録する。</t>
   </si>
   <si>
-    <t>複数回発生する可能性のあるイベントの発生について説明します。タイミングスケジュールは、イベントが発生することが予想または要求される時期を指定するために使用され、過去または進行中のイベントの概要を表すためにも使用できます。簡単にするために、タイミングコンポーネントの定義は「将来の」イベントとして表現されますが、そのようなコンポーネントは歴史的または進行中のイベントを説明するためにも使用できます。
-タイミングスケジュールは、イベントが発生したときのイベントおよび/または基準のリストであり、構造化された形式またはコードとして表現できます。イベントと繰り返し仕様の両方が提供される場合、イベントのリストは、繰り返し構造の情報の解釈として理解されるべきです。 / Describes the occurrence of an event that may occur multiple times. Timing schedules are used for specifying when events are expected or requested to occur, and may also be used to represent the summary of a past or ongoing event.  For simplicity, the definitions of Timing components are expressed as 'future' events, but such components can also be used to describe historic or ongoing events.
-A Timing schedule can be a list of events and/or criteria for when the event happens, which can be expressed in a structured form and/or as a code. When both event and a repeating specification are provided, the list of events should be understood as an interpretation of the information in the repeat structure.</t>
+    <t>この属性は、Dosage.Textが入力されると予想される間、常に埋め込まれるとは限りません。両方が入力されている場合、Dosage.textはDosage.timingの内容を反映する必要があります。 / This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
   </si>
   <si>
     <t>患者に薬を与えるためのタイミングスケジュール。このデータ型により、さまざまな式が可能になります。たとえば、「8時間ごと」。"一日に三回";「2011年12月23日から10日間の朝食の1/2の1/2：」;「2013年10月15日、2013年10月17日、2013年11月1日」。時には、総量 /持続時間として表される場合、レートは期間を意味する場合があります（たとえば、500ml / 2時間は2時間の期間を意味します）。ただし、レートが期間（250ml/hour）を意味しない場合、期間にわたって注入を伝えるためにタイミング.repeat.durationが必要です。 / The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
   </si>
   <si>
-    <t>QSET&lt;TS&gt; (GTS)</t>
+    <t>.effectiveTime</t>
   </si>
   <si>
     <t>Dosage.timing.id</t>
@@ -573,7 +571,7 @@
     <t>Timing.repeat</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 tim-1:期間がある場合は、期間単位が必要です / if there's a duration, there needs to be duration units {duration.empty() or durationUnit.exists()}tim-2:期間がある場合、期間単位が必要です / if there's a period, there needs to be period units {period.empty() or periodUnit.exists()}tim-4:期間は非陰性価値です / duration SHALL be a non-negative value {duration.exists() implies duration &gt;= 0}tim-5:期間は非陰性の価値です / period SHALL be a non-negative value {period.exists() implies period &gt;= 0}tim-6:期間がある場合、期間がなければなりません / If there's a periodMax, there must be a period {periodMax.empty() or period.exists()}tim-7:Hurtermaxがある場合、期間がなければなりません / If there's a durationMax, there must be a duration {durationMax.empty() or duration.exists()}tim-8:countmaxがある場合、カウントが必要です / If there's a countMax, there must be a count {countMax.empty() or count.exists()}tim-9:オフセットがある場合、c、cm、cd、cvではなく（c、cvではない）存在する必要があります。 / If there's an offset, there must be a when (and not C, CM, CD, CV) {offset.empty() or (when.exists() and ((when in ('C' | 'CM' | 'CD' | 'CV')).not()))}tim-10:時間がある場合、いつ、またはその逆もありません / If there's a timeOfDay, there cannot be a when, or vice versa {timeOfDay.empty() or when.empty()}</t>
   </si>
   <si>
@@ -1183,7 +1181,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1303,7 +1301,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1318,7 +1316,7 @@
     <t>Dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>Dosage.method.coding:unitDigit2.version</t>
@@ -1405,18 +1403,7 @@
     <t>1つの投与イベントで与えられた治療またはその他の物質の量。 / The amount of therapeutic or other substance given at one administration event.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>RXO-2, RXE-3</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.rate[x]</t>
@@ -1465,19 +1452,6 @@
 </t>
   </si>
   <si>
-    <t>単位時間内での薬剤の容量</t>
-  </si>
-  <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.rate[x]:rateRange</t>
   </si>
   <si>
@@ -1488,22 +1462,6 @@
 </t>
   </si>
   <si>
-    <t>範囲指定された時間の上限下限</t>
-  </si>
-  <si>
-    <t>時間の上限量、下限量の範囲を持っている。単位指定された数量を割り当てている。Low,Highの値は時間の単位当てはめる。</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>IVL&lt;QTY[not(type="TS")]&gt; [lowClosed="true" and highClosed="true"]or URG&lt;QTY[not(type="TS")]&gt;</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.rate[x]:rateQuantity</t>
   </si>
   <si>
@@ -1517,28 +1475,37 @@
     <t>投与速度(流量)を指定する単位は流量を表す単位（e.g. 量/時間)を指定する</t>
   </si>
   <si>
-    <t>使用のコンテキストは、これがどのような量であるか、したがってどのようなユニットを使用できるかを頻繁に定義する場合があります。使用のコンテキストは、コンパレータの値を制限する場合もあります。 / The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
     <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
     <t>単位時間当たりの投薬量の上限</t>
   </si>
   <si>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、「4時間ごとに最大8時間あたり2錠」。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example "2 tablets every 4 hours to a maximum of 8/day".</t>
+  </si>
+  <si>
     <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
+    <t>.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>RXO-23, RXE-19</t>
+  </si>
+  <si>
     <t>Dosage.maxDosePerAdministration</t>
   </si>
   <si>
     <t>1回あたりの投薬量の上限</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
+    <t>これは、上限があるときに投与量の補助として使用することを目的としています。たとえば、5〜10分間で1.5 mg/m2（最大2 mg）IVなどの最大量の体積領域に関連する用量に関連する用量は、1.5 mg/m2、最大2 mgのDosequantityになります。 / This is intended for use as an adjunct to the dosage when there is an upper cap.  For example, a body surface area related dose with a maximum amount, such as 1.5 mg/m2 (maximum 2 mg) IV over 5 – 10 minutes would have doseQuantity of 1.5 mg/m2 and maxDosePerAdministration of 2 mg.</t>
   </si>
   <si>
     <t>投与ごとの被験者に投与される可能性のある治療物質の最大総量。 / The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>not supported</t>
   </si>
   <si>
     <t>Dosage.maxDosePerLifetime</t>
@@ -3332,7 +3299,7 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>157</v>
@@ -3414,7 +3381,7 @@
         <v>162</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -10366,7 +10333,7 @@
         <v>76</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>445</v>
@@ -10439,24 +10406,24 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL79" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10479,19 +10446,19 @@
         <v>123</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -10528,17 +10495,17 @@
         <v>76</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -10553,21 +10520,21 @@
         <v>81</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>76</v>
@@ -10586,22 +10553,22 @@
         <v>76</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>76</v>
@@ -10650,7 +10617,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10659,27 +10626,27 @@
         <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>128</v>
+        <v>459</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D82" t="s" s="2">
         <v>76</v>
@@ -10698,22 +10665,22 @@
         <v>76</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>76</v>
@@ -10762,7 +10729,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10771,27 +10738,27 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>76</v>
@@ -10810,22 +10777,22 @@
         <v>76</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>76</v>
@@ -10874,7 +10841,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -10883,24 +10850,24 @@
         <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10920,22 +10887,22 @@
         <v>76</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>76</v>
@@ -10984,7 +10951,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -10993,24 +10960,24 @@
         <v>84</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>128</v>
+        <v>475</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11030,22 +10997,22 @@
         <v>76</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>445</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>76</v>
@@ -11094,7 +11061,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11103,24 +11070,24 @@
         <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>452</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11140,22 +11107,20 @@
         <v>76</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>445</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>76</v>
@@ -11204,7 +11169,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11213,16 +11178,16 @@
         <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>449</v>
+        <v>76</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>450</v>
+        <v>81</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>452</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -958,7 +958,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>
@@ -1821,17 +1821,17 @@
   <dimension ref="A1:AL86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.5" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.8515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.10546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.15234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="29.87890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.6640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.48828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.4375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1840,24 +1840,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="104.59765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.19140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="89.67578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.11328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6426,7 +6426,7 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -958,7 +958,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.2.0}
+    <t xml:space="preserve">Extension {bodySite|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -958,7 +958,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>
@@ -1088,7 +1088,7 @@
     <t>薬が投与される手法を説明するコード化された概念。 / A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -1410,7 +1410,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>薬剤の投与量速度</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationdosage-injection.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
